--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
-  <si>
-    <t>E2E Executive Overview</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+  <si>
+    <t>E2E Testing Executive Overview</t>
   </si>
   <si>
     <t/>
@@ -28,25 +28,16 @@
     <t>Failed Asserts</t>
   </si>
   <si>
-    <t>Skipped Asserts</t>
-  </si>
-  <si>
     <t>Verification Rate</t>
   </si>
   <si>
-    <t>99.57%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>52.24 seconds</t>
-  </si>
-  <si>
-    <t>Run Trigger Timestamp</t>
-  </si>
-  <si>
-    <t>2026-07-26T07:51:03.066Z</t>
+    <t>124.55 seconds</t>
   </si>
 </sst>
 </file>
@@ -64,17 +55,17 @@
     <font>
       <b/>
       <color rgb="FFFFFF"/>
-      <sz val="14"/>
-      <name val="Segoe UI"/>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -467,12 +458,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E10"/>
+  <dimension ref="A2:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -493,7 +484,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="3">
-        <v>470</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -506,7 +497,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
-        <v>468</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -519,7 +510,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -531,8 +522,8 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="3">
-        <v>0</v>
+      <c r="E7" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -540,50 +531,22 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>124.55 seconds</t>
+    <t>128.84 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.84 seconds</t>
+    <t>127.86 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.86 seconds</t>
+    <t>128.99 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.99 seconds</t>
+    <t>130.39 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>130.39 seconds</t>
+    <t>126.50 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.50 seconds</t>
+    <t>128.46 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.46 seconds</t>
+    <t>129.21 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.21 seconds</t>
+    <t>126.14 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.14 seconds</t>
+    <t>129.47 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.47 seconds</t>
+    <t>125.41 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.41 seconds</t>
+    <t>127.09 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.09 seconds</t>
+    <t>126.33 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.33 seconds</t>
+    <t>128.91 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.91 seconds</t>
+    <t>128.06 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.06 seconds</t>
+    <t>128.77 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.77 seconds</t>
+    <t>129.85 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.85 seconds</t>
+    <t>126.83 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.83 seconds</t>
+    <t>129.06 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.06 seconds</t>
+    <t>125.46 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.46 seconds</t>
+    <t>128.52 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.52 seconds</t>
+    <t>128.75 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.75 seconds</t>
+    <t>129.55 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.55 seconds</t>
+    <t>125.28 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.28 seconds</t>
+    <t>127.06 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.06 seconds</t>
+    <t>125.58 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.58 seconds</t>
+    <t>128.96 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.96 seconds</t>
+    <t>126.39 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.39 seconds</t>
+    <t>131.67 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>131.67 seconds</t>
+    <t>127.28 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.28 seconds</t>
+    <t>128.14 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.14 seconds</t>
+    <t>127.63 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.63 seconds</t>
+    <t>128.32 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.32 seconds</t>
+    <t>126.51 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.51 seconds</t>
+    <t>127.62 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.62 seconds</t>
+    <t>125.51 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.51 seconds</t>
+    <t>128.94 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.94 seconds</t>
+    <t>127.81 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.81 seconds</t>
+    <t>129.37 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.37 seconds</t>
+    <t>129.32 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.32 seconds</t>
+    <t>127.91 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.91 seconds</t>
+    <t>126.65 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.65 seconds</t>
+    <t>126.18 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.18 seconds</t>
+    <t>126.45 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.45 seconds</t>
+    <t>127.07 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.07 seconds</t>
+    <t>127.57 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.57 seconds</t>
+    <t>127.67 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.67 seconds</t>
+    <t>127.58 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.58 seconds</t>
+    <t>126.90 seconds</t>
   </si>
 </sst>
 </file>
